--- a/api/2/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/2/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14719" uniqueCount="6422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14824" uniqueCount="6469">
   <si>
     <t>code</t>
   </si>
@@ -4744,7 +4744,7 @@
     <t>FR-SIRET-77566669600015</t>
   </si>
   <si>
-    <t>SECOURS CATHOLIQUE - CARITAS FRANCE</t>
+    <t>Secours Catholique - Caritas France</t>
   </si>
   <si>
     <t>sccf</t>
@@ -9331,7 +9331,7 @@
     <t>NL-KVK-27367015</t>
   </si>
   <si>
-    <t>Netherlands Organisation for Scientific Research (NWO)</t>
+    <t>Dutch Research Council (NWO)</t>
   </si>
   <si>
     <t>nwo</t>
@@ -16810,7 +16810,7 @@
     <t>XM-OCHA-HPC6052</t>
   </si>
   <si>
-    <t>Himilo Relief and Development Association (HIRDA)</t>
+    <t>Himilo Relief and Development Association （HIRDA Somalia）</t>
   </si>
   <si>
     <t>hirda</t>
@@ -18685,6 +18685,24 @@
     <t>arin</t>
   </si>
   <si>
+    <t>IN-MHA-231660448</t>
+  </si>
+  <si>
+    <t>CENTRE FOR CHRONIC DISEASE CONTROL</t>
+  </si>
+  <si>
+    <t>ccdc_india</t>
+  </si>
+  <si>
+    <t>TG-NIF-1000047187</t>
+  </si>
+  <si>
+    <t>Women in Law and Development in Africa-Afrique de l’Ouest (WiLDAF-AO)</t>
+  </si>
+  <si>
+    <t>wildafao</t>
+  </si>
+  <si>
     <t>CH-FDJP-CHE365512867</t>
   </si>
   <si>
@@ -18721,6 +18739,84 @@
     <t>adra-sweden</t>
   </si>
   <si>
+    <t>GB-COH-07921860</t>
+  </si>
+  <si>
+    <t>Institutional Investors Group on Climate Change</t>
+  </si>
+  <si>
+    <t>iigcc</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-100493543</t>
+  </si>
+  <si>
+    <t>Associaçao de Protecao do Idosos de Tete</t>
+  </si>
+  <si>
+    <t>apite</t>
+  </si>
+  <si>
+    <t>GB-COH-12075030</t>
+  </si>
+  <si>
+    <t>Impact Knowledge Limited T/A Impact Capital Africa</t>
+  </si>
+  <si>
+    <t>Private Sector in Provider Country</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ica</t>
+  </si>
+  <si>
+    <t>GB-CHC-1111719</t>
+  </si>
+  <si>
+    <t>Anglo American Foundation</t>
+  </si>
+  <si>
+    <t>aaf</t>
+  </si>
+  <si>
+    <t>TZ-NNCB-00NGO00009862</t>
+  </si>
+  <si>
+    <t>Mtandao wa vikundi vya wakulima na wafugaji Nyancha</t>
+  </si>
+  <si>
+    <t>mviwanya</t>
+  </si>
+  <si>
+    <t>UA-EDR-45583070</t>
+  </si>
+  <si>
+    <t>VRUNA</t>
+  </si>
+  <si>
+    <t>vruna</t>
+  </si>
+  <si>
+    <t>XI-ROR-01ej9dk98</t>
+  </si>
+  <si>
+    <t>University of Melbourne</t>
+  </si>
+  <si>
+    <t>unimelb</t>
+  </si>
+  <si>
+    <t>TH-MOI-KhorThor3005</t>
+  </si>
+  <si>
+    <t>Thai Lawyers for Human Rights</t>
+  </si>
+  <si>
+    <t>tlhr</t>
+  </si>
+  <si>
     <t>SE-ON-252002-6135</t>
   </si>
   <si>
@@ -18782,6 +18878,51 @@
   </si>
   <si>
     <t>pangeaafrica</t>
+  </si>
+  <si>
+    <t>ZA-CIP-2025-956558-08</t>
+  </si>
+  <si>
+    <t>Impact Finance Facility NPC</t>
+  </si>
+  <si>
+    <t>iff-npc</t>
+  </si>
+  <si>
+    <t>ZA-CIT-9063151162</t>
+  </si>
+  <si>
+    <t>University of KwaZulu-Natal</t>
+  </si>
+  <si>
+    <t>ukzn</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-821-B</t>
+  </si>
+  <si>
+    <t>Diocese dos Libombos - ASA</t>
+  </si>
+  <si>
+    <t>asa</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-01567601-0001-43</t>
+  </si>
+  <si>
+    <t>Universidade Federal de Goiás</t>
+  </si>
+  <si>
+    <t>ufg</t>
+  </si>
+  <si>
+    <t>ET-CSA-0067</t>
+  </si>
+  <si>
+    <t>Tesfa Social &amp; Development Association</t>
+  </si>
+  <si>
+    <t>tsda</t>
   </si>
   <si>
     <t>CR-RPJ-3-002-248583</t>
@@ -19611,7 +19752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -66505,16 +66646,16 @@
         <v>9</v>
       </c>
       <c r="D2045" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2045" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2045" t="s">
         <v>6225</v>
       </c>
       <c r="G2045" t="s">
-        <v>72</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2046" spans="1:7">
@@ -66528,16 +66669,16 @@
         <v>9</v>
       </c>
       <c r="D2046" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E2046" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F2046" t="s">
         <v>6228</v>
       </c>
       <c r="G2046" t="s">
-        <v>436</v>
+        <v>4716</v>
       </c>
     </row>
     <row r="2047" spans="1:7">
@@ -66551,16 +66692,16 @@
         <v>9</v>
       </c>
       <c r="D2047" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2047" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2047" t="s">
         <v>6231</v>
       </c>
       <c r="G2047" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2048" spans="1:7">
@@ -66574,16 +66715,16 @@
         <v>9</v>
       </c>
       <c r="D2048" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E2048" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F2048" t="s">
         <v>6234</v>
       </c>
       <c r="G2048" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2049" spans="1:7">
@@ -66597,10 +66738,10 @@
         <v>9</v>
       </c>
       <c r="D2049" t="s">
-        <v>5212</v>
+        <v>175</v>
       </c>
       <c r="E2049" t="s">
-        <v>5213</v>
+        <v>176</v>
       </c>
       <c r="F2049" t="s">
         <v>6237</v>
@@ -66643,10 +66784,10 @@
         <v>9</v>
       </c>
       <c r="D2051" t="s">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="E2051" t="s">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="F2051" t="s">
         <v>6243</v>
@@ -66666,16 +66807,16 @@
         <v>9</v>
       </c>
       <c r="D2052" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2052" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2052" t="s">
         <v>6246</v>
       </c>
       <c r="G2052" t="s">
-        <v>47</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2053" spans="1:7">
@@ -66689,70 +66830,70 @@
         <v>9</v>
       </c>
       <c r="D2053" t="s">
-        <v>370</v>
+        <v>6249</v>
       </c>
       <c r="E2053" t="s">
-        <v>371</v>
+        <v>6250</v>
       </c>
       <c r="F2053" t="s">
-        <v>6249</v>
+        <v>6251</v>
       </c>
       <c r="G2053" t="s">
-        <v>2421</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2054" spans="1:7">
       <c r="A2054" t="s">
-        <v>6250</v>
+        <v>6252</v>
       </c>
       <c r="B2054" t="s">
-        <v>6251</v>
+        <v>6253</v>
       </c>
       <c r="C2054" t="s">
         <v>9</v>
       </c>
       <c r="D2054" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2054" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2054" t="s">
-        <v>6252</v>
+        <v>6254</v>
       </c>
       <c r="G2054" t="s">
-        <v>460</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2055" spans="1:7">
       <c r="A2055" t="s">
-        <v>6253</v>
+        <v>6255</v>
       </c>
       <c r="B2055" t="s">
-        <v>6254</v>
+        <v>6256</v>
       </c>
       <c r="C2055" t="s">
         <v>9</v>
       </c>
       <c r="D2055" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E2055" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="F2055" t="s">
-        <v>6255</v>
+        <v>6257</v>
       </c>
       <c r="G2055" t="s">
-        <v>705</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2056" spans="1:7">
       <c r="A2056" t="s">
-        <v>6256</v>
+        <v>6258</v>
       </c>
       <c r="B2056" t="s">
-        <v>6257</v>
+        <v>6259</v>
       </c>
       <c r="C2056" t="s">
         <v>9</v>
@@ -66764,93 +66905,99 @@
         <v>176</v>
       </c>
       <c r="F2056" t="s">
-        <v>6258</v>
+        <v>6260</v>
       </c>
       <c r="G2056" t="s">
-        <v>2917</v>
+        <v>927</v>
       </c>
     </row>
     <row r="2057" spans="1:7">
       <c r="A2057" t="s">
-        <v>6259</v>
+        <v>6261</v>
       </c>
       <c r="B2057" t="s">
-        <v>6260</v>
+        <v>6262</v>
       </c>
       <c r="C2057" t="s">
         <v>9</v>
       </c>
+      <c r="D2057" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2057" t="s">
+        <v>371</v>
+      </c>
       <c r="F2057" t="s">
-        <v>6261</v>
+        <v>6263</v>
       </c>
       <c r="G2057" t="s">
-        <v>358</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2058" spans="1:7">
       <c r="A2058" t="s">
-        <v>6262</v>
+        <v>6264</v>
       </c>
       <c r="B2058" t="s">
-        <v>6263</v>
+        <v>6265</v>
       </c>
       <c r="C2058" t="s">
         <v>9</v>
       </c>
       <c r="D2058" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2058" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2058" t="s">
-        <v>6264</v>
+        <v>6266</v>
       </c>
       <c r="G2058" t="s">
-        <v>633</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="2059" spans="1:7">
       <c r="A2059" t="s">
-        <v>6265</v>
+        <v>6267</v>
       </c>
       <c r="B2059" t="s">
-        <v>6266</v>
+        <v>6268</v>
       </c>
       <c r="C2059" t="s">
         <v>9</v>
       </c>
       <c r="D2059" t="s">
-        <v>16</v>
+        <v>5212</v>
       </c>
       <c r="E2059" t="s">
-        <v>17</v>
+        <v>5213</v>
       </c>
       <c r="F2059" t="s">
-        <v>6267</v>
+        <v>6269</v>
       </c>
       <c r="G2059" t="s">
-        <v>633</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2060" spans="1:7">
       <c r="A2060" t="s">
-        <v>6268</v>
+        <v>6270</v>
       </c>
       <c r="B2060" t="s">
-        <v>6269</v>
+        <v>6271</v>
       </c>
       <c r="C2060" t="s">
         <v>9</v>
       </c>
       <c r="D2060" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2060" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2060" t="s">
-        <v>6270</v>
+        <v>6272</v>
       </c>
       <c r="G2060" t="s">
         <v>47</v>
@@ -66858,45 +67005,45 @@
     </row>
     <row r="2061" spans="1:7">
       <c r="A2061" t="s">
-        <v>6271</v>
+        <v>6273</v>
       </c>
       <c r="B2061" t="s">
-        <v>6272</v>
+        <v>6274</v>
       </c>
       <c r="C2061" t="s">
         <v>9</v>
       </c>
       <c r="D2061" t="s">
-        <v>6029</v>
+        <v>370</v>
       </c>
       <c r="E2061" t="s">
-        <v>6030</v>
+        <v>371</v>
       </c>
       <c r="F2061" t="s">
-        <v>6273</v>
+        <v>6275</v>
       </c>
       <c r="G2061" t="s">
-        <v>436</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2062" spans="1:7">
       <c r="A2062" t="s">
-        <v>6274</v>
+        <v>6276</v>
       </c>
       <c r="B2062" t="s">
-        <v>6275</v>
+        <v>6277</v>
       </c>
       <c r="C2062" t="s">
         <v>9</v>
       </c>
       <c r="D2062" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2062" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2062" t="s">
-        <v>6276</v>
+        <v>6278</v>
       </c>
       <c r="G2062" t="s">
         <v>47</v>
@@ -66904,159 +67051,171 @@
     </row>
     <row r="2063" spans="1:7">
       <c r="A2063" t="s">
-        <v>6277</v>
+        <v>6279</v>
       </c>
       <c r="B2063" t="s">
-        <v>6278</v>
+        <v>6280</v>
       </c>
       <c r="C2063" t="s">
         <v>9</v>
       </c>
+      <c r="D2063" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2063" t="s">
+        <v>371</v>
+      </c>
       <c r="F2063" t="s">
-        <v>6279</v>
+        <v>6281</v>
       </c>
       <c r="G2063" t="s">
-        <v>47</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="2064" spans="1:7">
       <c r="A2064" t="s">
-        <v>6280</v>
+        <v>6282</v>
       </c>
       <c r="B2064" t="s">
-        <v>6281</v>
+        <v>6283</v>
       </c>
       <c r="C2064" t="s">
         <v>9</v>
       </c>
       <c r="D2064" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E2064" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="F2064" t="s">
-        <v>6282</v>
+        <v>6284</v>
       </c>
       <c r="G2064" t="s">
-        <v>4560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2065" spans="1:7">
       <c r="A2065" t="s">
-        <v>6283</v>
+        <v>6285</v>
       </c>
       <c r="B2065" t="s">
-        <v>6284</v>
+        <v>6286</v>
       </c>
       <c r="C2065" t="s">
         <v>9</v>
       </c>
       <c r="D2065" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2065" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2065" t="s">
-        <v>6285</v>
+        <v>6287</v>
       </c>
       <c r="G2065" t="s">
-        <v>402</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2066" spans="1:7">
       <c r="A2066" t="s">
-        <v>6286</v>
+        <v>6288</v>
       </c>
       <c r="B2066" t="s">
-        <v>6287</v>
+        <v>6289</v>
       </c>
       <c r="C2066" t="s">
         <v>9</v>
       </c>
       <c r="D2066" t="s">
-        <v>22</v>
+        <v>5212</v>
       </c>
       <c r="E2066" t="s">
-        <v>23</v>
+        <v>5213</v>
       </c>
       <c r="F2066" t="s">
-        <v>6288</v>
+        <v>6290</v>
       </c>
       <c r="G2066" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2067" spans="1:7">
       <c r="A2067" t="s">
-        <v>6289</v>
+        <v>6291</v>
       </c>
       <c r="B2067" t="s">
-        <v>6290</v>
+        <v>6292</v>
       </c>
       <c r="C2067" t="s">
         <v>9</v>
       </c>
       <c r="D2067" t="s">
-        <v>31</v>
+        <v>370</v>
       </c>
       <c r="E2067" t="s">
-        <v>32</v>
+        <v>371</v>
       </c>
       <c r="F2067" t="s">
-        <v>6291</v>
+        <v>6293</v>
       </c>
       <c r="G2067" t="s">
-        <v>481</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2068" spans="1:7">
       <c r="A2068" t="s">
-        <v>6292</v>
+        <v>6294</v>
       </c>
       <c r="B2068" t="s">
-        <v>6293</v>
+        <v>6295</v>
       </c>
       <c r="C2068" t="s">
         <v>9</v>
       </c>
       <c r="D2068" t="s">
-        <v>5212</v>
+        <v>6029</v>
       </c>
       <c r="E2068" t="s">
-        <v>5213</v>
+        <v>6030</v>
       </c>
       <c r="F2068" t="s">
-        <v>6294</v>
+        <v>6296</v>
       </c>
       <c r="G2068" t="s">
-        <v>6295</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2069" spans="1:7">
       <c r="A2069" t="s">
-        <v>6296</v>
+        <v>6297</v>
       </c>
       <c r="B2069" t="s">
-        <v>6297</v>
+        <v>6298</v>
       </c>
       <c r="C2069" t="s">
         <v>9</v>
       </c>
+      <c r="D2069" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>371</v>
+      </c>
       <c r="F2069" t="s">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="G2069" t="s">
-        <v>47</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="2070" spans="1:7">
       <c r="A2070" t="s">
-        <v>6299</v>
+        <v>6300</v>
       </c>
       <c r="B2070" t="s">
-        <v>6300</v>
+        <v>6301</v>
       </c>
       <c r="C2070" t="s">
         <v>9</v>
@@ -67068,122 +67227,116 @@
         <v>176</v>
       </c>
       <c r="F2070" t="s">
-        <v>6301</v>
+        <v>6302</v>
       </c>
       <c r="G2070" t="s">
-        <v>683</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="2071" spans="1:7">
       <c r="A2071" t="s">
-        <v>6302</v>
+        <v>6303</v>
       </c>
       <c r="B2071" t="s">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="C2071" t="s">
         <v>9</v>
       </c>
       <c r="D2071" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2071" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2071" t="s">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="G2071" t="s">
-        <v>503</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="2072" spans="1:7">
       <c r="A2072" t="s">
-        <v>6305</v>
+        <v>6306</v>
       </c>
       <c r="B2072" t="s">
-        <v>4425</v>
+        <v>6307</v>
       </c>
       <c r="C2072" t="s">
         <v>9</v>
       </c>
-      <c r="D2072" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2072" t="s">
-        <v>176</v>
-      </c>
       <c r="F2072" t="s">
-        <v>6306</v>
+        <v>6308</v>
       </c>
       <c r="G2072" t="s">
-        <v>599</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2073" spans="1:7">
       <c r="A2073" t="s">
-        <v>6307</v>
+        <v>6309</v>
       </c>
       <c r="B2073" t="s">
-        <v>6308</v>
+        <v>6310</v>
       </c>
       <c r="C2073" t="s">
         <v>9</v>
       </c>
       <c r="D2073" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2073" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2073" t="s">
-        <v>6309</v>
+        <v>6311</v>
       </c>
       <c r="G2073" t="s">
-        <v>436</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2074" spans="1:7">
       <c r="A2074" t="s">
-        <v>6310</v>
+        <v>6312</v>
       </c>
       <c r="B2074" t="s">
-        <v>6311</v>
+        <v>6313</v>
       </c>
       <c r="C2074" t="s">
         <v>9</v>
       </c>
       <c r="D2074" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="E2074" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F2074" t="s">
-        <v>6312</v>
+        <v>6314</v>
       </c>
       <c r="G2074" t="s">
-        <v>87</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2075" spans="1:7">
       <c r="A2075" t="s">
-        <v>6313</v>
+        <v>6315</v>
       </c>
       <c r="B2075" t="s">
-        <v>6314</v>
+        <v>6316</v>
       </c>
       <c r="C2075" t="s">
         <v>9</v>
       </c>
       <c r="D2075" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2075" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2075" t="s">
-        <v>6315</v>
+        <v>6317</v>
       </c>
       <c r="G2075" t="s">
         <v>47</v>
@@ -67191,33 +67344,33 @@
     </row>
     <row r="2076" spans="1:7">
       <c r="A2076" t="s">
-        <v>6316</v>
+        <v>6318</v>
       </c>
       <c r="B2076" t="s">
-        <v>6317</v>
+        <v>6319</v>
       </c>
       <c r="C2076" t="s">
         <v>9</v>
       </c>
       <c r="D2076" t="s">
-        <v>22</v>
+        <v>6029</v>
       </c>
       <c r="E2076" t="s">
-        <v>23</v>
+        <v>6030</v>
       </c>
       <c r="F2076" t="s">
-        <v>6318</v>
+        <v>6320</v>
       </c>
       <c r="G2076" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2077" spans="1:7">
       <c r="A2077" t="s">
-        <v>6319</v>
+        <v>6321</v>
       </c>
       <c r="B2077" t="s">
-        <v>6320</v>
+        <v>6322</v>
       </c>
       <c r="C2077" t="s">
         <v>9</v>
@@ -67229,156 +67382,156 @@
         <v>176</v>
       </c>
       <c r="F2077" t="s">
-        <v>6321</v>
+        <v>6323</v>
       </c>
       <c r="G2077" t="s">
-        <v>2028</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2078" spans="1:7">
       <c r="A2078" t="s">
-        <v>6322</v>
+        <v>6324</v>
       </c>
       <c r="B2078" t="s">
-        <v>6323</v>
+        <v>6325</v>
       </c>
       <c r="C2078" t="s">
         <v>9</v>
       </c>
-      <c r="D2078" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2078" t="s">
-        <v>371</v>
-      </c>
       <c r="F2078" t="s">
-        <v>6324</v>
+        <v>6326</v>
       </c>
       <c r="G2078" t="s">
-        <v>599</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2079" spans="1:7">
       <c r="A2079" t="s">
-        <v>6325</v>
+        <v>6327</v>
       </c>
       <c r="B2079" t="s">
-        <v>6326</v>
+        <v>6328</v>
       </c>
       <c r="C2079" t="s">
         <v>9</v>
       </c>
       <c r="D2079" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2079" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2079" t="s">
-        <v>6327</v>
+        <v>6329</v>
       </c>
       <c r="G2079" t="s">
-        <v>1951</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="2080" spans="1:7">
       <c r="A2080" t="s">
-        <v>6328</v>
+        <v>6330</v>
       </c>
       <c r="B2080" t="s">
-        <v>6329</v>
+        <v>6331</v>
       </c>
       <c r="C2080" t="s">
         <v>9</v>
       </c>
+      <c r="D2080" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>176</v>
+      </c>
       <c r="F2080" t="s">
-        <v>6330</v>
+        <v>6332</v>
       </c>
       <c r="G2080" t="s">
-        <v>705</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2081" spans="1:7">
       <c r="A2081" t="s">
-        <v>6331</v>
+        <v>6333</v>
       </c>
       <c r="B2081" t="s">
-        <v>6332</v>
+        <v>6334</v>
       </c>
       <c r="C2081" t="s">
         <v>9</v>
       </c>
       <c r="D2081" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2081" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2081" t="s">
-        <v>6333</v>
+        <v>6335</v>
       </c>
       <c r="G2081" t="s">
-        <v>470</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2082" spans="1:7">
       <c r="A2082" t="s">
-        <v>6334</v>
+        <v>6336</v>
       </c>
       <c r="B2082" t="s">
-        <v>6335</v>
+        <v>6337</v>
       </c>
       <c r="C2082" t="s">
         <v>9</v>
       </c>
       <c r="D2082" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E2082" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2082" t="s">
-        <v>6336</v>
+        <v>6338</v>
       </c>
       <c r="G2082" t="s">
-        <v>34</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2083" spans="1:7">
       <c r="A2083" t="s">
-        <v>6337</v>
+        <v>6339</v>
       </c>
       <c r="B2083" t="s">
-        <v>6338</v>
+        <v>6340</v>
       </c>
       <c r="C2083" t="s">
         <v>9</v>
       </c>
       <c r="D2083" t="s">
-        <v>370</v>
+        <v>5212</v>
       </c>
       <c r="E2083" t="s">
-        <v>371</v>
+        <v>5213</v>
       </c>
       <c r="F2083" t="s">
-        <v>6339</v>
+        <v>6341</v>
       </c>
       <c r="G2083" t="s">
-        <v>34</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="2084" spans="1:7">
       <c r="A2084" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
       <c r="B2084" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
       <c r="C2084" t="s">
         <v>9</v>
       </c>
       <c r="F2084" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
       <c r="G2084" t="s">
         <v>47</v>
@@ -67386,10 +67539,10 @@
     </row>
     <row r="2085" spans="1:7">
       <c r="A2085" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
       <c r="B2085" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="C2085" t="s">
         <v>9</v>
@@ -67401,41 +67554,41 @@
         <v>176</v>
       </c>
       <c r="F2085" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
       <c r="G2085" t="s">
-        <v>2533</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2086" spans="1:7">
       <c r="A2086" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
       <c r="B2086" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
       <c r="C2086" t="s">
         <v>9</v>
       </c>
       <c r="D2086" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2086" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2086" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
       <c r="G2086" t="s">
-        <v>47</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2087" spans="1:7">
       <c r="A2087" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
       <c r="B2087" t="s">
-        <v>6350</v>
+        <v>4425</v>
       </c>
       <c r="C2087" t="s">
         <v>9</v>
@@ -67447,150 +67600,156 @@
         <v>176</v>
       </c>
       <c r="F2087" t="s">
-        <v>6351</v>
+        <v>6353</v>
       </c>
       <c r="G2087" t="s">
-        <v>47</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2088" spans="1:7">
       <c r="A2088" t="s">
-        <v>6352</v>
+        <v>6354</v>
       </c>
       <c r="B2088" t="s">
-        <v>6353</v>
+        <v>6355</v>
       </c>
       <c r="C2088" t="s">
         <v>9</v>
       </c>
       <c r="D2088" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2088" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2088" t="s">
-        <v>6354</v>
+        <v>6356</v>
       </c>
       <c r="G2088" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2089" spans="1:7">
       <c r="A2089" t="s">
-        <v>6355</v>
+        <v>6357</v>
       </c>
       <c r="B2089" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="C2089" t="s">
         <v>9</v>
       </c>
       <c r="D2089" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2089" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2089" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="G2089" t="s">
-        <v>927</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2090" spans="1:7">
       <c r="A2090" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
       <c r="B2090" t="s">
-        <v>6359</v>
+        <v>6361</v>
       </c>
       <c r="C2090" t="s">
         <v>9</v>
       </c>
+      <c r="D2090" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>32</v>
+      </c>
       <c r="F2090" t="s">
-        <v>6360</v>
+        <v>6362</v>
       </c>
       <c r="G2090" t="s">
-        <v>436</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2091" spans="1:7">
       <c r="A2091" t="s">
-        <v>6361</v>
+        <v>6363</v>
       </c>
       <c r="B2091" t="s">
-        <v>6362</v>
+        <v>6364</v>
       </c>
       <c r="C2091" t="s">
         <v>9</v>
       </c>
       <c r="D2091" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2091" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2091" t="s">
-        <v>6363</v>
+        <v>6365</v>
       </c>
       <c r="G2091" t="s">
-        <v>3677</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2092" spans="1:7">
       <c r="A2092" t="s">
-        <v>6364</v>
+        <v>6366</v>
       </c>
       <c r="B2092" t="s">
-        <v>6365</v>
+        <v>6367</v>
       </c>
       <c r="C2092" t="s">
         <v>9</v>
       </c>
       <c r="D2092" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2092" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2092" t="s">
-        <v>6366</v>
+        <v>6368</v>
       </c>
       <c r="G2092" t="s">
-        <v>25</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="2093" spans="1:7">
       <c r="A2093" t="s">
-        <v>6367</v>
+        <v>6369</v>
       </c>
       <c r="B2093" t="s">
-        <v>6368</v>
+        <v>6370</v>
       </c>
       <c r="C2093" t="s">
         <v>9</v>
       </c>
       <c r="D2093" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2093" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2093" t="s">
-        <v>6369</v>
+        <v>6371</v>
       </c>
       <c r="G2093" t="s">
-        <v>1935</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2094" spans="1:7">
       <c r="A2094" t="s">
-        <v>6370</v>
+        <v>6372</v>
       </c>
       <c r="B2094" t="s">
-        <v>6371</v>
+        <v>6373</v>
       </c>
       <c r="C2094" t="s">
         <v>9</v>
@@ -67602,139 +67761,133 @@
         <v>176</v>
       </c>
       <c r="F2094" t="s">
-        <v>6372</v>
+        <v>6374</v>
       </c>
       <c r="G2094" t="s">
-        <v>6295</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="2095" spans="1:7">
       <c r="A2095" t="s">
-        <v>6373</v>
+        <v>6375</v>
       </c>
       <c r="B2095" t="s">
-        <v>6374</v>
+        <v>6376</v>
       </c>
       <c r="C2095" t="s">
         <v>9</v>
       </c>
-      <c r="D2095" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2095" t="s">
-        <v>176</v>
-      </c>
       <c r="F2095" t="s">
-        <v>6375</v>
+        <v>6377</v>
       </c>
       <c r="G2095" t="s">
-        <v>6204</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2096" spans="1:7">
       <c r="A2096" t="s">
-        <v>6376</v>
+        <v>6378</v>
       </c>
       <c r="B2096" t="s">
-        <v>6377</v>
+        <v>6379</v>
       </c>
       <c r="C2096" t="s">
         <v>9</v>
       </c>
+      <c r="D2096" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2096" t="s">
+        <v>371</v>
+      </c>
       <c r="F2096" t="s">
-        <v>6378</v>
+        <v>6380</v>
       </c>
       <c r="G2096" t="s">
-        <v>47</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2097" spans="1:7">
       <c r="A2097" t="s">
-        <v>6379</v>
+        <v>6381</v>
       </c>
       <c r="B2097" t="s">
-        <v>6380</v>
+        <v>6382</v>
       </c>
       <c r="C2097" t="s">
         <v>9</v>
       </c>
       <c r="D2097" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E2097" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F2097" t="s">
-        <v>6381</v>
+        <v>6383</v>
       </c>
       <c r="G2097" t="s">
-        <v>358</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2098" spans="1:7">
       <c r="A2098" t="s">
-        <v>6382</v>
+        <v>6384</v>
       </c>
       <c r="B2098" t="s">
-        <v>6383</v>
+        <v>6385</v>
       </c>
       <c r="C2098" t="s">
         <v>9</v>
       </c>
       <c r="D2098" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2098" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2098" t="s">
-        <v>6384</v>
+        <v>6386</v>
       </c>
       <c r="G2098" t="s">
-        <v>927</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2099" spans="1:7">
       <c r="A2099" t="s">
-        <v>6385</v>
+        <v>6387</v>
       </c>
       <c r="B2099" t="s">
-        <v>6386</v>
+        <v>6388</v>
       </c>
       <c r="C2099" t="s">
         <v>9</v>
       </c>
-      <c r="D2099" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2099" t="s">
-        <v>371</v>
-      </c>
       <c r="F2099" t="s">
-        <v>6387</v>
+        <v>6389</v>
       </c>
       <c r="G2099" t="s">
-        <v>1706</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2100" spans="1:7">
       <c r="A2100" t="s">
-        <v>6388</v>
+        <v>6390</v>
       </c>
       <c r="B2100" t="s">
-        <v>6389</v>
+        <v>6391</v>
       </c>
       <c r="C2100" t="s">
         <v>9</v>
       </c>
       <c r="D2100" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E2100" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="F2100" t="s">
-        <v>6390</v>
+        <v>6392</v>
       </c>
       <c r="G2100" t="s">
         <v>2533</v>
@@ -67742,10 +67895,10 @@
     </row>
     <row r="2101" spans="1:7">
       <c r="A2101" t="s">
-        <v>6391</v>
+        <v>6393</v>
       </c>
       <c r="B2101" t="s">
-        <v>6392</v>
+        <v>6394</v>
       </c>
       <c r="C2101" t="s">
         <v>9</v>
@@ -67757,41 +67910,41 @@
         <v>176</v>
       </c>
       <c r="F2101" t="s">
-        <v>6393</v>
+        <v>6395</v>
       </c>
       <c r="G2101" t="s">
-        <v>2837</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2102" spans="1:7">
       <c r="A2102" t="s">
-        <v>6394</v>
+        <v>6396</v>
       </c>
       <c r="B2102" t="s">
-        <v>6395</v>
+        <v>6397</v>
       </c>
       <c r="C2102" t="s">
         <v>9</v>
       </c>
       <c r="D2102" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2102" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2102" t="s">
-        <v>6396</v>
+        <v>6398</v>
       </c>
       <c r="G2102" t="s">
-        <v>5837</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2103" spans="1:7">
       <c r="A2103" t="s">
-        <v>6397</v>
+        <v>6399</v>
       </c>
       <c r="B2103" t="s">
-        <v>6398</v>
+        <v>6400</v>
       </c>
       <c r="C2103" t="s">
         <v>9</v>
@@ -67803,7 +67956,7 @@
         <v>32</v>
       </c>
       <c r="F2103" t="s">
-        <v>6399</v>
+        <v>6401</v>
       </c>
       <c r="G2103" t="s">
         <v>47</v>
@@ -67811,102 +67964,96 @@
     </row>
     <row r="2104" spans="1:7">
       <c r="A2104" t="s">
-        <v>6400</v>
+        <v>6402</v>
       </c>
       <c r="B2104" t="s">
-        <v>6401</v>
+        <v>6403</v>
       </c>
       <c r="C2104" t="s">
         <v>9</v>
       </c>
       <c r="D2104" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2104" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2104" t="s">
-        <v>6402</v>
+        <v>6404</v>
       </c>
       <c r="G2104" t="s">
-        <v>47</v>
+        <v>927</v>
       </c>
     </row>
     <row r="2105" spans="1:7">
       <c r="A2105" t="s">
-        <v>6403</v>
+        <v>6405</v>
       </c>
       <c r="B2105" t="s">
-        <v>6404</v>
+        <v>6406</v>
       </c>
       <c r="C2105" t="s">
         <v>9</v>
       </c>
-      <c r="D2105" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2105" t="s">
-        <v>32</v>
-      </c>
       <c r="F2105" t="s">
-        <v>6405</v>
+        <v>6407</v>
       </c>
       <c r="G2105" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2106" spans="1:7">
       <c r="A2106" t="s">
-        <v>6406</v>
+        <v>6408</v>
       </c>
       <c r="B2106" t="s">
-        <v>6407</v>
+        <v>6409</v>
       </c>
       <c r="C2106" t="s">
         <v>9</v>
       </c>
       <c r="D2106" t="s">
-        <v>22</v>
+        <v>370</v>
       </c>
       <c r="E2106" t="s">
-        <v>23</v>
+        <v>371</v>
       </c>
       <c r="F2106" t="s">
-        <v>6408</v>
+        <v>6410</v>
       </c>
       <c r="G2106" t="s">
-        <v>47</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="2107" spans="1:7">
       <c r="A2107" t="s">
-        <v>6409</v>
+        <v>6411</v>
       </c>
       <c r="B2107" t="s">
-        <v>6410</v>
+        <v>6412</v>
       </c>
       <c r="C2107" t="s">
         <v>9</v>
       </c>
       <c r="D2107" t="s">
-        <v>290</v>
+        <v>31</v>
       </c>
       <c r="E2107" t="s">
-        <v>291</v>
+        <v>32</v>
       </c>
       <c r="F2107" t="s">
-        <v>6411</v>
+        <v>6413</v>
       </c>
       <c r="G2107" t="s">
-        <v>436</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2108" spans="1:7">
       <c r="A2108" t="s">
-        <v>6412</v>
+        <v>6414</v>
       </c>
       <c r="B2108" t="s">
-        <v>6413</v>
+        <v>6415</v>
       </c>
       <c r="C2108" t="s">
         <v>9</v>
@@ -67918,78 +68065,417 @@
         <v>176</v>
       </c>
       <c r="F2108" t="s">
-        <v>6414</v>
+        <v>6416</v>
       </c>
       <c r="G2108" t="s">
-        <v>358</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="2109" spans="1:7">
       <c r="A2109" t="s">
-        <v>6415</v>
+        <v>6417</v>
       </c>
       <c r="B2109" t="s">
-        <v>6416</v>
+        <v>6418</v>
       </c>
       <c r="C2109" t="s">
         <v>9</v>
       </c>
       <c r="D2109" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2109" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2109" t="s">
-        <v>6417</v>
+        <v>6419</v>
       </c>
       <c r="G2109" t="s">
-        <v>47</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="2110" spans="1:7">
       <c r="A2110" t="s">
-        <v>6418</v>
+        <v>6420</v>
       </c>
       <c r="B2110" t="s">
-        <v>5025</v>
+        <v>6421</v>
       </c>
       <c r="C2110" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D2110" t="s">
-        <v>290</v>
+        <v>175</v>
       </c>
       <c r="E2110" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="F2110" t="s">
-        <v>5026</v>
+        <v>6422</v>
       </c>
       <c r="G2110" t="s">
-        <v>1706</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="2111" spans="1:7">
       <c r="A2111" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
       <c r="B2111" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
       <c r="C2111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2111" t="s">
+        <v>6425</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:7">
+      <c r="A2112" t="s">
+        <v>6426</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>6427</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2112" t="s">
+        <v>6428</v>
+      </c>
+      <c r="G2112" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:7">
+      <c r="A2113" t="s">
+        <v>6429</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>6430</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2113" t="s">
+        <v>6431</v>
+      </c>
+      <c r="G2113" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:7">
+      <c r="A2114" t="s">
+        <v>6432</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>6433</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2114" t="s">
+        <v>6434</v>
+      </c>
+      <c r="G2114" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:7">
+      <c r="A2115" t="s">
+        <v>6435</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>6436</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2115" t="s">
+        <v>6437</v>
+      </c>
+      <c r="G2115" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:7">
+      <c r="A2116" t="s">
+        <v>6438</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>6439</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2116" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2116" t="s">
+        <v>6440</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:7">
+      <c r="A2117" t="s">
+        <v>6441</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>6442</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2117" t="s">
+        <v>6443</v>
+      </c>
+      <c r="G2117" t="s">
+        <v>5837</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:7">
+      <c r="A2118" t="s">
+        <v>6444</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>6445</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2118" t="s">
+        <v>6446</v>
+      </c>
+      <c r="G2118" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7">
+      <c r="A2119" t="s">
+        <v>6447</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>6448</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2119" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>6449</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7">
+      <c r="A2120" t="s">
+        <v>6450</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>6451</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2120" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2120" t="s">
+        <v>6452</v>
+      </c>
+      <c r="G2120" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7">
+      <c r="A2121" t="s">
+        <v>6453</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>6454</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2121" t="s">
+        <v>6455</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7">
+      <c r="A2122" t="s">
+        <v>6456</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>6457</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2122" t="s">
+        <v>6458</v>
+      </c>
+      <c r="G2122" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7">
+      <c r="A2123" t="s">
+        <v>6459</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2123" t="s">
+        <v>6461</v>
+      </c>
+      <c r="G2123" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7">
+      <c r="A2124" t="s">
+        <v>6462</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>6463</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2124" t="s">
+        <v>6464</v>
+      </c>
+      <c r="G2124" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7">
+      <c r="A2125" t="s">
+        <v>6465</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C2125" t="s">
         <v>42</v>
       </c>
-      <c r="D2111" t="s">
+      <c r="D2125" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2125" t="s">
+        <v>5026</v>
+      </c>
+      <c r="G2125" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7">
+      <c r="A2126" t="s">
+        <v>6466</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>6467</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2126" t="s">
         <v>370</v>
       </c>
-      <c r="E2111" t="s">
+      <c r="E2126" t="s">
         <v>371</v>
       </c>
-      <c r="F2111" t="s">
-        <v>6421</v>
-      </c>
-      <c r="G2111" t="s">
+      <c r="F2126" t="s">
+        <v>6468</v>
+      </c>
+      <c r="G2126" t="s">
         <v>524</v>
       </c>
     </row>
